--- a/Data/RemapDrafts/YelanRemapDraft.xlsx
+++ b/Data/RemapDrafts/YelanRemapDraft.xlsx
@@ -6,14 +6,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 Yelan to YelanTranquil" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 Yelan to Tranquil (tool)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilBody to Yelan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilBang to Yelan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilEye to Yelan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credits" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 Yelan to YelanTranquil" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 Yelan to Tranquil (tool)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilBody to Yelan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilBang to Yelan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.7 TranquilEye to Yelan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V5.7 Yelan to YelanTranquil'!$A$1:$F$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V5.7 Yelan to YelanTranquil'!$A$1:$F$114</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -40,6 +41,22 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="20"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,10 +79,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,6 +532,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>AlbertGold#2696</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>🦴🧭 The Vertex Group Cartographer: The 32nd member of The Council</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1727,7 +1795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3603,7 +3671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5701,7 +5769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5975,7 +6043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
